--- a/marketing/results/Overlay results (live).xlsx
+++ b/marketing/results/Overlay results (live).xlsx
@@ -1120,6 +1120,13 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>Bets at $10 or more from 11 to 15 Sep are excluded: our ratings over-priced long shots until the 15 Sep fix.</t>
+        </is>
+      </c>
+    </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="12" t="inlineStr">
         <is>

--- a/marketing/results/Overlay results (live).xlsx
+++ b/marketing/results/Overlay results (live).xlsx
@@ -190,7 +190,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -296,6 +296,7 @@
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -9798,7 +9799,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6">
+      <c r="A6" s="41">
         <f>IFERROR(QUERY(Data!A2:O20000,"select * where Col1 is not null order by Col1 desc, Col2, Col3",0),"Loading results")</f>
         <v/>
       </c>
@@ -10032,7 +10033,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6">
+      <c r="A6" s="41">
         <f>IFERROR(QUERY(Data!A2:O20000,"select * where Col1 is not null and Col6 = 'Bet' order by Col1 desc, Col2, Col3",0),"Loading results")</f>
         <v/>
       </c>
@@ -10266,7 +10267,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6">
+      <c r="A6" s="41">
         <f>IFERROR(QUERY(Data!A2:O20000,"select * where Col1 is not null and Col6 = 'Lay' order by Col1 desc, Col2, Col3",0),"Loading results")</f>
         <v/>
       </c>

--- a/marketing/results/Overlay results (live).xlsx
+++ b/marketing/results/Overlay results (live).xlsx
@@ -1089,19 +1089,19 @@
     <row r="8" ht="20" customHeight="1"/>
     <row r="9" ht="20" customHeight="1">
       <c r="B9" s="9">
-        <f>IFERROR(COUNTIFS(Data!$M$2:$M$20000,"Win")+COUNTIFS(Data!$M$2:$M$20000,"Loss")&amp;" settled, "&amp;TEXT(COUNTIFS(Data!$M$2:$M$20000,"Win")/(COUNTIFS(Data!$M$2:$M$20000,"Win")+COUNTIFS(Data!$M$2:$M$20000,"Loss")),"0%")&amp;" strike, "&amp;TEXT(B7/SUM(Data!$O$2:$O$20000),"+0.0%;-0.0%")&amp;" ROI","")</f>
+        <f>IFERROR(COUNTIFS(Data!$M$2:$M$20000,"Win")+COUNTIFS(Data!$M$2:$M$20000,"Loss")&amp;" settled, "&amp;TEXT(COUNTIFS(Data!$M$2:$M$20000,"Win")/(COUNTIFS(Data!$M$2:$M$20000,"Win")+COUNTIFS(Data!$M$2:$M$20000,"Loss")),"0%")&amp;" strike, "&amp;TEXT(B7/SUM(Data!$K$2:$K$20000),"+0.0%;-0.0%")&amp;" POT","")</f>
         <v/>
       </c>
       <c r="C9" s="1" t="n"/>
       <c r="D9" s="1" t="n"/>
       <c r="E9" s="10">
-        <f>IFERROR(COUNTIFS(Data!$M$2:$M$20000,"Win",Data!$F$2:$F$20000,"Bet")+COUNTIFS(Data!$M$2:$M$20000,"Loss",Data!$F$2:$F$20000,"Bet")&amp;" settled, "&amp;TEXT(COUNTIFS(Data!$M$2:$M$20000,"Win",Data!$F$2:$F$20000,"Bet")/(COUNTIFS(Data!$M$2:$M$20000,"Win",Data!$F$2:$F$20000,"Bet")+COUNTIFS(Data!$M$2:$M$20000,"Loss",Data!$F$2:$F$20000,"Bet")),"0%")&amp;" strike, "&amp;TEXT(E7/SUMIFS(Data!$O$2:$O$20000,Data!$F$2:$F$20000,"Bet"),"+0.0%;-0.0%")&amp;" ROI","")</f>
+        <f>IFERROR(COUNTIFS(Data!$M$2:$M$20000,"Win",Data!$F$2:$F$20000,"Bet")+COUNTIFS(Data!$M$2:$M$20000,"Loss",Data!$F$2:$F$20000,"Bet")&amp;" settled, "&amp;TEXT(COUNTIFS(Data!$M$2:$M$20000,"Win",Data!$F$2:$F$20000,"Bet")/(COUNTIFS(Data!$M$2:$M$20000,"Win",Data!$F$2:$F$20000,"Bet")+COUNTIFS(Data!$M$2:$M$20000,"Loss",Data!$F$2:$F$20000,"Bet")),"0%")&amp;" strike, "&amp;TEXT(E7/SUMIFS(Data!$K$2:$K$20000,Data!$F$2:$F$20000,"Bet"),"+0.0%;-0.0%")&amp;" POT","")</f>
         <v/>
       </c>
       <c r="F9" s="6" t="n"/>
       <c r="G9" s="6" t="n"/>
       <c r="H9" s="10">
-        <f>IFERROR(COUNTIFS(Data!$M$2:$M$20000,"Win",Data!$F$2:$F$20000,"Lay")+COUNTIFS(Data!$M$2:$M$20000,"Loss",Data!$F$2:$F$20000,"Lay")&amp;" settled, "&amp;TEXT(COUNTIFS(Data!$M$2:$M$20000,"Win",Data!$F$2:$F$20000,"Lay")/(COUNTIFS(Data!$M$2:$M$20000,"Win",Data!$F$2:$F$20000,"Lay")+COUNTIFS(Data!$M$2:$M$20000,"Loss",Data!$F$2:$F$20000,"Lay")),"0%")&amp;" strike, "&amp;TEXT(H7/SUMIFS(Data!$O$2:$O$20000,Data!$F$2:$F$20000,"Lay"),"+0.0%;-0.0%")&amp;" ROI","")</f>
+        <f>IFERROR(COUNTIFS(Data!$M$2:$M$20000,"Win",Data!$F$2:$F$20000,"Lay")+COUNTIFS(Data!$M$2:$M$20000,"Loss",Data!$F$2:$F$20000,"Lay")&amp;" settled, "&amp;TEXT(COUNTIFS(Data!$M$2:$M$20000,"Win",Data!$F$2:$F$20000,"Lay")/(COUNTIFS(Data!$M$2:$M$20000,"Win",Data!$F$2:$F$20000,"Lay")+COUNTIFS(Data!$M$2:$M$20000,"Loss",Data!$F$2:$F$20000,"Lay")),"0%")&amp;" strike, "&amp;TEXT(H7/SUMIFS(Data!$K$2:$K$20000,Data!$F$2:$F$20000,"Lay"),"+0.0%;-0.0%")&amp;" POT","")</f>
         <v/>
       </c>
       <c r="I9" s="6" t="n"/>
@@ -1117,7 +1117,7 @@
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>A lay wins one unit when the horse loses and risks the price less one. ROI is profit over units at risk. Calls on scratched horses and abandoned races are void and left out.</t>
+          <t>A lay wins one unit when the horse loses. POT is units won over units staked: one a call, a tenth on a Way. Calls on scratched horses and abandoned races are void and left out.</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
-          <t>At risk (u)</t>
+          <t>Staked (u)</t>
         </is>
       </c>
       <c r="H15" s="13" t="inlineStr">
         <is>
-          <t>ROI</t>
+          <t>POT</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
         <v/>
       </c>
       <c r="G16" s="18">
-        <f>SUM(Data!$O$2:$O$20000)</f>
+        <f>SUM(Data!$K$2:$K$20000)</f>
         <v/>
       </c>
       <c r="H16" s="19">
@@ -1235,7 +1235,7 @@
         <v/>
       </c>
       <c r="G17" s="24">
-        <f>SUMIFS(Data!$O$2:$O$20000,Data!$F$2:$F$20000,"Bet")</f>
+        <f>SUMIFS(Data!$K$2:$K$20000,Data!$F$2:$F$20000,"Bet")</f>
         <v/>
       </c>
       <c r="H17" s="25">
@@ -1270,7 +1270,7 @@
         <v/>
       </c>
       <c r="G18" s="18">
-        <f>SUMIFS(Data!$O$2:$O$20000,Data!$F$2:$F$20000,"Lay")</f>
+        <f>SUMIFS(Data!$K$2:$K$20000,Data!$F$2:$F$20000,"Lay")</f>
         <v/>
       </c>
       <c r="H18" s="19">
@@ -1318,12 +1318,12 @@
       </c>
       <c r="G21" s="13" t="inlineStr">
         <is>
-          <t>At risk (u)</t>
+          <t>Staked (u)</t>
         </is>
       </c>
       <c r="H21" s="13" t="inlineStr">
         <is>
-          <t>ROI</t>
+          <t>POT</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
         <v/>
       </c>
       <c r="G22" s="18">
-        <f>SUMIFS(Data!$O$2:$O$20000,Data!$G$2:$G$20000,"Prime")</f>
+        <f>SUMIFS(Data!$K$2:$K$20000,Data!$G$2:$G$20000,"Prime")</f>
         <v/>
       </c>
       <c r="H22" s="19">
@@ -1389,7 +1389,7 @@
         <v/>
       </c>
       <c r="G23" s="24">
-        <f>SUMIFS(Data!$O$2:$O$20000,Data!$G$2:$G$20000,"Bet")</f>
+        <f>SUMIFS(Data!$K$2:$K$20000,Data!$G$2:$G$20000,"Bet")</f>
         <v/>
       </c>
       <c r="H23" s="25">
@@ -1424,7 +1424,7 @@
         <v/>
       </c>
       <c r="G24" s="18">
-        <f>SUMIFS(Data!$O$2:$O$20000,Data!$G$2:$G$20000,"Way")</f>
+        <f>SUMIFS(Data!$K$2:$K$20000,Data!$G$2:$G$20000,"Way")</f>
         <v/>
       </c>
       <c r="H24" s="19">
@@ -1459,7 +1459,7 @@
         <v/>
       </c>
       <c r="G25" s="24">
-        <f>SUMIFS(Data!$O$2:$O$20000,Data!$G$2:$G$20000,"Lay")</f>
+        <f>SUMIFS(Data!$K$2:$K$20000,Data!$G$2:$G$20000,"Lay")</f>
         <v/>
       </c>
       <c r="H25" s="25">
@@ -1507,12 +1507,12 @@
       </c>
       <c r="G28" s="13" t="inlineStr">
         <is>
-          <t>At risk (u)</t>
+          <t>Staked (u)</t>
         </is>
       </c>
       <c r="H28" s="13" t="inlineStr">
         <is>
-          <t>ROI</t>
+          <t>POT</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
         <v/>
       </c>
       <c r="G29" s="18">
-        <f>IF($A29="","",SUMIFS(Data!$O$2:$O$20000,Data!$A$2:$A$20000,"&gt;="&amp;$A29,Data!$A$2:$A$20000,"&lt;"&amp;($A29+7)))</f>
+        <f>IF($A29="","",SUMIFS(Data!$K$2:$K$20000,Data!$A$2:$A$20000,"&gt;="&amp;$A29,Data!$A$2:$A$20000,"&lt;"&amp;($A29+7)))</f>
         <v/>
       </c>
       <c r="H29" s="19">
@@ -1581,7 +1581,7 @@
         <v/>
       </c>
       <c r="G30" s="24">
-        <f>IF($A30="","",SUMIFS(Data!$O$2:$O$20000,Data!$A$2:$A$20000,"&gt;="&amp;$A30,Data!$A$2:$A$20000,"&lt;"&amp;($A30+7)))</f>
+        <f>IF($A30="","",SUMIFS(Data!$K$2:$K$20000,Data!$A$2:$A$20000,"&gt;="&amp;$A30,Data!$A$2:$A$20000,"&lt;"&amp;($A30+7)))</f>
         <v/>
       </c>
       <c r="H30" s="25">
@@ -1640,7 +1640,7 @@
         <v/>
       </c>
       <c r="G31" s="18">
-        <f>IF($A31="","",SUMIFS(Data!$O$2:$O$20000,Data!$A$2:$A$20000,"&gt;="&amp;$A31,Data!$A$2:$A$20000,"&lt;"&amp;($A31+7)))</f>
+        <f>IF($A31="","",SUMIFS(Data!$K$2:$K$20000,Data!$A$2:$A$20000,"&gt;="&amp;$A31,Data!$A$2:$A$20000,"&lt;"&amp;($A31+7)))</f>
         <v/>
       </c>
       <c r="H31" s="19">
@@ -1694,7 +1694,7 @@
         <v/>
       </c>
       <c r="G32" s="24">
-        <f>IF($A32="","",SUMIFS(Data!$O$2:$O$20000,Data!$A$2:$A$20000,"&gt;="&amp;$A32,Data!$A$2:$A$20000,"&lt;"&amp;($A32+7)))</f>
+        <f>IF($A32="","",SUMIFS(Data!$K$2:$K$20000,Data!$A$2:$A$20000,"&gt;="&amp;$A32,Data!$A$2:$A$20000,"&lt;"&amp;($A32+7)))</f>
         <v/>
       </c>
       <c r="H32" s="25">
@@ -1745,7 +1745,7 @@
         <v/>
       </c>
       <c r="G33" s="18">
-        <f>IF($A33="","",SUMIFS(Data!$O$2:$O$20000,Data!$A$2:$A$20000,"&gt;="&amp;$A33,Data!$A$2:$A$20000,"&lt;"&amp;($A33+7)))</f>
+        <f>IF($A33="","",SUMIFS(Data!$K$2:$K$20000,Data!$A$2:$A$20000,"&gt;="&amp;$A33,Data!$A$2:$A$20000,"&lt;"&amp;($A33+7)))</f>
         <v/>
       </c>
       <c r="H33" s="19">
@@ -1796,7 +1796,7 @@
         <v/>
       </c>
       <c r="G34" s="24">
-        <f>IF($A34="","",SUMIFS(Data!$O$2:$O$20000,Data!$A$2:$A$20000,"&gt;="&amp;$A34,Data!$A$2:$A$20000,"&lt;"&amp;($A34+7)))</f>
+        <f>IF($A34="","",SUMIFS(Data!$K$2:$K$20000,Data!$A$2:$A$20000,"&gt;="&amp;$A34,Data!$A$2:$A$20000,"&lt;"&amp;($A34+7)))</f>
         <v/>
       </c>
       <c r="H34" s="25">
@@ -1847,7 +1847,7 @@
         <v/>
       </c>
       <c r="G35" s="18">
-        <f>IF($A35="","",SUMIFS(Data!$O$2:$O$20000,Data!$A$2:$A$20000,"&gt;="&amp;$A35,Data!$A$2:$A$20000,"&lt;"&amp;($A35+7)))</f>
+        <f>IF($A35="","",SUMIFS(Data!$K$2:$K$20000,Data!$A$2:$A$20000,"&gt;="&amp;$A35,Data!$A$2:$A$20000,"&lt;"&amp;($A35+7)))</f>
         <v/>
       </c>
       <c r="H35" s="19">
@@ -1898,7 +1898,7 @@
         <v/>
       </c>
       <c r="G36" s="24">
-        <f>IF($A36="","",SUMIFS(Data!$O$2:$O$20000,Data!$A$2:$A$20000,"&gt;="&amp;$A36,Data!$A$2:$A$20000,"&lt;"&amp;($A36+7)))</f>
+        <f>IF($A36="","",SUMIFS(Data!$K$2:$K$20000,Data!$A$2:$A$20000,"&gt;="&amp;$A36,Data!$A$2:$A$20000,"&lt;"&amp;($A36+7)))</f>
         <v/>
       </c>
       <c r="H36" s="25">
@@ -1949,7 +1949,7 @@
         <v/>
       </c>
       <c r="G37" s="18">
-        <f>IF($A37="","",SUMIFS(Data!$O$2:$O$20000,Data!$A$2:$A$20000,"&gt;="&amp;$A37,Data!$A$2:$A$20000,"&lt;"&amp;($A37+7)))</f>
+        <f>IF($A37="","",SUMIFS(Data!$K$2:$K$20000,Data!$A$2:$A$20000,"&gt;="&amp;$A37,Data!$A$2:$A$20000,"&lt;"&amp;($A37+7)))</f>
         <v/>
       </c>
       <c r="H37" s="19">
@@ -2000,7 +2000,7 @@
         <v/>
       </c>
       <c r="G38" s="24">
-        <f>IF($A38="","",SUMIFS(Data!$O$2:$O$20000,Data!$A$2:$A$20000,"&gt;="&amp;$A38,Data!$A$2:$A$20000,"&lt;"&amp;($A38+7)))</f>
+        <f>IF($A38="","",SUMIFS(Data!$K$2:$K$20000,Data!$A$2:$A$20000,"&gt;="&amp;$A38,Data!$A$2:$A$20000,"&lt;"&amp;($A38+7)))</f>
         <v/>
       </c>
       <c r="H38" s="25">
@@ -2051,7 +2051,7 @@
         <v/>
       </c>
       <c r="G39" s="18">
-        <f>IF($A39="","",SUMIFS(Data!$O$2:$O$20000,Data!$A$2:$A$20000,"&gt;="&amp;$A39,Data!$A$2:$A$20000,"&lt;"&amp;($A39+7)))</f>
+        <f>IF($A39="","",SUMIFS(Data!$K$2:$K$20000,Data!$A$2:$A$20000,"&gt;="&amp;$A39,Data!$A$2:$A$20000,"&lt;"&amp;($A39+7)))</f>
         <v/>
       </c>
       <c r="H39" s="19">
@@ -2102,7 +2102,7 @@
         <v/>
       </c>
       <c r="G40" s="24">
-        <f>IF($A40="","",SUMIFS(Data!$O$2:$O$20000,Data!$A$2:$A$20000,"&gt;="&amp;$A40,Data!$A$2:$A$20000,"&lt;"&amp;($A40+7)))</f>
+        <f>IF($A40="","",SUMIFS(Data!$K$2:$K$20000,Data!$A$2:$A$20000,"&gt;="&amp;$A40,Data!$A$2:$A$20000,"&lt;"&amp;($A40+7)))</f>
         <v/>
       </c>
       <c r="H40" s="25">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="O5" s="13" t="inlineStr">
         <is>
-          <t>At risk (u)</t>
+          <t>Liability (u)</t>
         </is>
       </c>
     </row>
@@ -10028,7 +10028,7 @@
       </c>
       <c r="O5" s="13" t="inlineStr">
         <is>
-          <t>At risk (u)</t>
+          <t>Liability (u)</t>
         </is>
       </c>
     </row>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="O5" s="13" t="inlineStr">
         <is>
-          <t>At risk (u)</t>
+          <t>Liability (u)</t>
         </is>
       </c>
     </row>
